--- a/data/trans_dic/VUL_MENTALCOM-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/VUL_MENTALCOM-Estudios-trans_dic.xlsx
@@ -583,40 +583,40 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>0.1151788946503906</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0</v>
+        <v>0.1892031736872829</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>0.03888882513181108</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>0.05929837358910743</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>0.206715403206164</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0</v>
+        <v>0.3953496590703196</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>0.1021159953678668</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>0.1164282661639655</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>0.1739678242379251</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>0.3023698090158354</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>0.07422691895882873</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>0.09341291624121079</v>
       </c>
     </row>
     <row r="5">
@@ -626,18 +626,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="n">
+        <v>0.07408593595603767</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.122160957173987</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.0223844184346913</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.04101427774008896</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.1734522994477771</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.3207959270657496</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.07577435943796054</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0.09316348491613584</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.150730076872635</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.2426650779880572</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.05791191325190669</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.07602507334808252</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -646,18 +670,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n">
+        <v>0.1608068449666916</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.2805614191322385</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.06262982112015952</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.08530867339515646</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.2439508444470821</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.4813772504445903</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.1352144064925666</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0.1435966525078313</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.2028958491350938</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.3640208686242248</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.09496621104054366</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.1122867005924245</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -671,40 +719,40 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0</v>
+        <v>0.05754243440160384</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0</v>
+        <v>0.1738697370855312</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>0.03983920986975445</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0</v>
+        <v>0.03852852285355939</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0</v>
+        <v>0.1286602751053116</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0</v>
+        <v>0.2821654505366361</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>0.06963015448956623</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>0.06942008459141237</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>0.09278839110430821</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>0.2278139596588949</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0</v>
+        <v>0.05488890162118029</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0</v>
+        <v>0.05386761347261999</v>
       </c>
     </row>
     <row r="8">
@@ -714,18 +762,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="n">
+        <v>0.04395740822217986</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.1488693538065561</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.02867927452754788</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.03151341403043441</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.1113705050584794</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.2508191714051654</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.05584009958551895</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0.05883668464223693</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.08166475496603627</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.2059211249322993</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0.04567481204981944</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0.04728297119656281</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -734,18 +806,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="n">
+        <v>0.07490671847487965</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.2051826203555324</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.05174945082417911</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.04743811212659205</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.1482148495356986</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.3198010919822831</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.08551482073284519</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0.08045577024254658</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.1053135885364058</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0.2497368925784064</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0.06481241317103584</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0.06106736009745468</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -759,40 +855,40 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>0.06129365679146182</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0</v>
+        <v>0.1103455479614747</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>0.01986382861802647</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>0.02768785620169576</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>0.07030256681049118</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0</v>
+        <v>0.2336799198888088</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>0.03173230289507139</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0</v>
+        <v>0.04842603540712542</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>0.06572609268134755</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0</v>
+        <v>0.1791202616782528</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0</v>
+        <v>0.02603405162984686</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0</v>
+        <v>0.03942210119200575</v>
       </c>
     </row>
     <row r="11">
@@ -802,18 +898,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="n">
+        <v>0.03982075838569096</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.08551813658435731</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.01020806398582229</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.01695603541242004</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.0500660607585016</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.2006883286570081</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.02037431750021711</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0.03678137741651531</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.05085258771707006</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0.1577277748230248</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0.01811747752790085</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0.03096133227994306</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -822,18 +942,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="n">
+        <v>0.08814549878468449</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.1419550456216354</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.03642817595115093</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.04127025517377948</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.09420223708860574</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.2709778682598271</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.05027775776456795</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0.0649659727822878</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.08429272374773103</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0.2054624356596143</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0.03690996225642499</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0.04834830064105521</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -847,40 +991,40 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>0.06504904841875185</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0</v>
+        <v>0.1551100848116601</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>0.0342310403759659</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>0.03821781651231058</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>0.1294756422246154</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0</v>
+        <v>0.2819659278485412</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>0.06468491072818566</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0</v>
+        <v>0.0704750907472015</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>0.09836187831322768</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0</v>
+        <v>0.2219467733622759</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0</v>
+        <v>0.04999669705613454</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0</v>
+        <v>0.0552673062821537</v>
       </c>
     </row>
     <row r="14">
@@ -890,18 +1034,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="n">
+        <v>0.0532210671797345</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.136937831169902</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.02668245961271891</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.03179745310710741</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.1161405658323668</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.2568738417363733</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.05418295244084156</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0.06284541846493684</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.08870589094823349</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.2048966027505189</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.04387184504047516</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.04961139960309961</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -910,18 +1078,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="n">
+        <v>0.07877483939101662</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.1768381364731997</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.04341579737743659</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.04504296321849301</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.1432299127570965</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.3049562923243359</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.07422688801340388</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0.07913132035369352</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0.1076058979437461</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0.2378445532328708</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0.05707392971621437</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0.06071504039686838</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1094,40 +1286,40 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5">
@@ -1138,40 +1330,40 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0</v>
+        <v>23373</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>18647</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>6998</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>4352</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>75308</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0</v>
+        <v>47423</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0</v>
+        <v>23284</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0</v>
+        <v>12664</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0</v>
+        <v>98681</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0</v>
+        <v>66070</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0</v>
+        <v>30283</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0</v>
+        <v>17016</v>
       </c>
     </row>
     <row r="6">
@@ -1181,18 +1373,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>15034</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12040</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4028</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3010</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>63190</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>38480</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>17278</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>10134</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>85500</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>53024</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>23627</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>13849</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -1201,18 +1417,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="n">
+        <v>32633</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>27651</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>11271</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6260</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>88873</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>57742</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>30832</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>15620</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>115090</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>79541</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>38744</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>20454</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1226,40 +1466,40 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
@@ -1270,40 +1510,40 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0</v>
+        <v>64297</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>62047</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>28954</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>15852</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0</v>
+        <v>141254</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0</v>
+        <v>99939</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0</v>
+        <v>51663</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0</v>
+        <v>28171</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0</v>
+        <v>205551</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0</v>
+        <v>161986</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0</v>
+        <v>80617</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0</v>
+        <v>44023</v>
       </c>
     </row>
     <row r="10">
@@ -1313,18 +1553,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr"/>
-      <c r="N10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>49117</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>53125</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>20843</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>12966</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>122272</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>88836</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>41432</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>23876</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>180909</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>146419</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>67084</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>38642</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -1333,18 +1597,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>83699</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>73221</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>37610</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>19518</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>162723</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>113269</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>63449</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>32649</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>233298</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>177574</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>95192</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>49907</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1358,40 +1646,40 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -1402,40 +1690,40 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>29137</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0</v>
+        <v>24785</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>6794</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>4404</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0</v>
+        <v>32368</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0</v>
+        <v>66162</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0</v>
+        <v>11752</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0</v>
+        <v>10038</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0</v>
+        <v>61505</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0</v>
+        <v>90947</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>0</v>
+        <v>18546</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0</v>
+        <v>14442</v>
       </c>
     </row>
     <row r="14">
@@ -1445,18 +1733,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="n">
+        <v>18930</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>19208</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>3491</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>2697</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>23051</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>56821</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>7546</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>7624</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>47587</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>80085</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>12907</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>11342</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -1465,18 +1777,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr"/>
-      <c r="N15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="n">
+        <v>41902</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>31885</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>12459</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6564</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>43371</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>76722</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>18621</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>13467</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>78879</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>104322</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>26294</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>17712</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1490,40 +1826,40 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17">
@@ -1534,40 +1870,40 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0</v>
+        <v>116807</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>105479</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>42746</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>24608</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>248930</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>213524</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0</v>
+        <v>86700</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0</v>
+        <v>50873</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0</v>
+        <v>365737</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0</v>
+        <v>319002</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0</v>
+        <v>129446</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0</v>
+        <v>75481</v>
       </c>
     </row>
     <row r="18">
@@ -1577,18 +1913,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>95568</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>93121</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>33320</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>20474</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>223292</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>194522</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>72624</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>45366</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>329833</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>294496</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>113588</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>67756</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1597,18 +1957,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr"/>
-      <c r="N19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
+        <v>141455</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>120254</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>54215</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>29002</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>275374</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>230934</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>99490</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>57122</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>400109</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>341852</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>147770</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>82921</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
